--- a/data/reports/2024-04-22/2024-04-22_duplicates.xlsx
+++ b/data/reports/2024-04-22/2024-04-22_duplicates.xlsx
@@ -85,6 +85,49 @@
     <t>filing_url</t>
   </si>
   <si>
+    <t>RMD0004807</t>
+  </si>
+  <si>
+    <t>e-vergent.com, LLC</t>
+  </si>
+  <si>
+    <t>2524 76th St
+Franksville WI 53126</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>United States of America</t>
+  </si>
+  <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>Shawn Tarlo</t>
+  </si>
+  <si>
+    <t>Technical Support Lead</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>2628983786</t>
+  </si>
+  <si>
+    <t>Complete STIR/SHAKEN Implementation</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>2024-04-02</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0004801</t>
   </si>
   <si>
@@ -95,53 +138,10 @@
 Franksville Wisconsin 53126</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>United States of America</t>
-  </si>
-  <si>
-    <t>none</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=949115a61bc13c102eb2a82fe54bcb0c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004807</t>
-  </si>
-  <si>
-    <t>e-vergent.com, LLC</t>
-  </si>
-  <si>
-    <t>2524 76th St
-Franksville WI 53126</t>
-  </si>
-  <si>
-    <t>Shawn Tarlo</t>
-  </si>
-  <si>
-    <t>Technical Support Lead</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>2628983786</t>
-  </si>
-  <si>
-    <t>Complete STIR/SHAKEN Implementation</t>
-  </si>
-  <si>
-    <t>2024-04-02</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
+    <t>RMD0004723</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -157,6 +157,12 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005813</t>
+  </si>
+  <si>
     <t>Glenn Dalgliesh</t>
   </si>
   <si>
@@ -173,12 +179,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004723</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -252,7 +252,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -268,6 +268,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -275,24 +293,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009084</t>
@@ -422,7 +422,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6239f4c21bcdf41002beea82f54bcb2a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004849</t>
+    <t>RMD0004806</t>
   </si>
   <si>
     <t>Smartbiz Telecom, LLC</t>
@@ -433,6 +433,15 @@
 Miami FL 33126</t>
   </si>
   <si>
+    <t>2023-03-24</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004849</t>
+  </si>
+  <si>
     <t>Eduardo Borrero</t>
   </si>
   <si>
@@ -449,15 +458,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=beda02fb1bc5f05064c4426de54bcb94&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004806</t>
-  </si>
-  <si>
-    <t>2023-03-24</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005786</t>
@@ -544,10 +544,30 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=494bb99d1bcdf0109294113d9c4bcb26&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008297</t>
+  </si>
+  <si>
+    <t>GloTell US Corp.</t>
+  </si>
+  <si>
+    <t>1830 S Ocean Drive
+Suite 902
+Halladale Beach FL 33009</t>
+  </si>
+  <si>
+    <t>Alina Karpova</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>9548354110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0002900</t>
-  </si>
-  <si>
-    <t>GloTell US Corp.</t>
   </si>
   <si>
     <t>1001 North Federal Hwy
@@ -574,27 +594,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0a82aeaf1b7430507ccf20ecac4bcb54&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008297</t>
-  </si>
-  <si>
-    <t>1830 S Ocean Drive
-Suite 902
-Halladale Beach FL 33009</t>
-  </si>
-  <si>
-    <t>Alina Karpova</t>
-  </si>
-  <si>
-    <t>Administration</t>
-  </si>
-  <si>
-    <t>9548354110</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ffdd33cb1bfe781093d3a820f54bcb29&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004110</t>
+    <t>RMD0004738</t>
   </si>
   <si>
     <t>RyTel, LLC</t>
@@ -605,12 +605,6 @@
 Salt Lake City UT 84119</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0004738</t>
-  </si>
-  <si>
     <t>Lamont Snarr</t>
   </si>
   <si>
@@ -628,6 +622,12 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9650dd421bcd38102eb2a82fe54bcb46&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004110</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=64046a611bc1b4102eb2a82fe54bcb32&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005139</t>
@@ -715,7 +715,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003053</t>
+    <t>RMD0009640</t>
   </si>
   <si>
     <t>The Kalson Inc Limited</t>
@@ -725,22 +725,22 @@
  UB10 0AD UXBRIDGE, United Kingdom</t>
   </si>
   <si>
+    <t>Anum Rasheed Kalson</t>
+  </si>
+  <si>
+    <t>'+92-3222100249</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003053</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=73375fbb1b30b0507ccf20ecac4bcb1c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009640</t>
-  </si>
-  <si>
-    <t>Anum Rasheed Kalson</t>
-  </si>
-  <si>
-    <t>'+92-3222100249</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -751,32 +751,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -796,7 +770,33 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007384</t>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0003705</t>
   </si>
   <si>
     <t>Axkan Consultores S. de R.L. de C.V.</t>
@@ -809,6 +809,12 @@
     <t>Mexico</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007384</t>
+  </si>
+  <si>
     <t>Juan Carlos Bravo Abarca</t>
   </si>
   <si>
@@ -818,13 +824,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=47035e5e1b7eb4109ac2ea04bc4bcbb1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003705</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
+    <t>RMD0008577</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -834,28 +834,28 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>BatchDialer</t>
+  </si>
+  <si>
+    <t>Ivo Draginov</t>
+  </si>
+  <si>
+    <t>Product Manager</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>6026220397</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005040</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008577</t>
-  </si>
-  <si>
-    <t>BatchDialer</t>
-  </si>
-  <si>
-    <t>Ivo Draginov</t>
-  </si>
-  <si>
-    <t>Product Manager</t>
-  </si>
-  <si>
-    <t>Operations</t>
-  </si>
-  <si>
-    <t>6026220397</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005461</t>
@@ -1008,7 +1008,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3acc71c31b2a305064c4426de54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008125</t>
+    <t>RMD0008123</t>
   </si>
   <si>
     <t>Hansen Network Solutions &amp; Services</t>
@@ -1019,6 +1019,12 @@
 Las Vegas NV 89128</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008125</t>
+  </si>
+  <si>
     <t>JR Jarmillo</t>
   </si>
   <si>
@@ -1031,13 +1037,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9277fe1b7a3810dcd1ed3be54bcb40&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008123</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=3cc1fbbe1b7a3810dcd1ed3be54bcbe8&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007575</t>
+    <t>RMD0007626</t>
   </si>
   <si>
     <t>Turcios Parada SA</t>
@@ -1050,13 +1050,13 @@
     <t>El Salvador</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007575</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007626</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5b6a75a61b3af410680f657ae54bcbbd&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007696</t>
@@ -1078,7 +1078,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1088,6 +1088,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1101,12 +1107,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1140,7 +1140,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1150,16 +1150,16 @@
 Greensboro NC 27401</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
+    <t>RMD0008611</t>
   </si>
   <si>
     <t>Liberty Wealth Planners</t>
@@ -1169,6 +1169,18 @@
  110065 Dehli, India</t>
   </si>
   <si>
+    <t>Bangladesh</t>
+  </si>
+  <si>
+    <t>Nobe</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
     <t>India</t>
   </si>
   <si>
@@ -1179,18 +1191,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008611</t>
-  </si>
-  <si>
-    <t>Bangladesh</t>
-  </si>
-  <si>
-    <t>Nobe</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008610</t>
@@ -1224,7 +1224,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9bf181421b0b3050003c43f1f54bcbe8&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008755</t>
+    <t>RMD0008798</t>
   </si>
   <si>
     <t>Aspire Holdings Group LLC</t>
@@ -1237,30 +1237,30 @@
     <t>AspirePBX</t>
   </si>
   <si>
+    <t>CP Short</t>
+  </si>
+  <si>
+    <t>Member</t>
+  </si>
+  <si>
+    <t>Partner</t>
+  </si>
+  <si>
+    <t>6023888700</t>
+  </si>
+  <si>
+    <t>725</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008755</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=82b1054a1b0f30508d57ecace54bcbda&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008798</t>
-  </si>
-  <si>
-    <t>CP Short</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>Partner</t>
-  </si>
-  <si>
-    <t>6023888700</t>
-  </si>
-  <si>
-    <t>725</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9cda6ace1b8f30505eb762cfe54bcb49&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0008787</t>
   </si>
   <si>
@@ -1288,7 +1288,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=29f1aec61b0f3050003c43f1f54bcba5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009161</t>
+    <t>RMD0009160</t>
   </si>
   <si>
     <t>MCE Systems</t>
@@ -1298,16 +1298,16 @@
 Irvine CA 92604</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009161</t>
+  </si>
+  <si>
     <t>9497014500</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=2338b76a1b577410503110ad9c4bcb43&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009160</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8975f3e61b577410503110ad9c4bcbcf&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0009453</t>
@@ -5806,40 +5806,56 @@
       <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
+      <c r="J3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
+      <c r="Q3" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R3" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S3" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U3" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="V3" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B4" s="1">
         <v>16082927</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>26</v>
@@ -5856,40 +5872,24 @@
       <c r="I4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="N4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O4" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S4" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U4" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U4" s="1"/>
       <c r="V4" s="1" t="s">
         <v>40</v>
       </c>
@@ -5920,28 +5920,14 @@
         <v>45</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="M5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O5" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -5949,16 +5935,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -5982,14 +5968,28 @@
         <v>45</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
+      <c r="J6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
+      <c r="Q6" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6046,10 +6046,10 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>26</v>
@@ -6112,10 +6112,10 @@
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>26</v>
@@ -6144,7 +6144,7 @@
         <v>69</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>70</v>
@@ -6169,7 +6169,7 @@
         <v>26</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="1" t="s">
@@ -6190,7 +6190,7 @@
         <v>74</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>70</v>
@@ -6215,7 +6215,7 @@
         <v>26</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U10" s="1"/>
       <c r="V10" s="1" t="s">
@@ -6262,12 +6262,14 @@
       <c r="O11" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>26</v>
@@ -6275,14 +6277,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6309,7 +6313,7 @@
         <v>80</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>78</v>
@@ -6318,16 +6322,14 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>87</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>26</v>
@@ -6335,9 +6337,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>88</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>89</v>
       </c>
@@ -6356,7 +6356,7 @@
         <v>92</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>70</v>
@@ -6381,7 +6381,7 @@
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
@@ -6435,7 +6435,7 @@
         <v>101</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
@@ -6489,7 +6489,7 @@
         <v>26</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U15" s="1"/>
       <c r="V15" s="1" t="s">
@@ -6542,10 +6542,10 @@
         <v>114</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S16" s="1" t="s">
         <v>26</v>
@@ -6597,7 +6597,7 @@
         <v>26</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U17" s="1"/>
       <c r="V17" s="1" t="s">
@@ -6641,7 +6641,7 @@
         <v>26</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U18" s="1"/>
       <c r="V18" s="1" t="s">
@@ -6671,13 +6671,13 @@
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>125</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>26</v>
@@ -6743,7 +6743,7 @@
         <v>26</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U20" s="1"/>
       <c r="V20" s="1" t="s">
@@ -6772,47 +6772,33 @@
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="V21" s="1" t="s">
         <v>134</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:22">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B22" s="1">
         <v>26116624</v>
@@ -6832,22 +6818,36 @@
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
+      <c r="J22" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>139</v>
+      </c>
       <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
+      <c r="Q22" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R22" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>140</v>
@@ -6870,7 +6870,7 @@
         <v>144</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>70</v>
@@ -6893,7 +6893,7 @@
         <v>26</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U23" s="1"/>
       <c r="V23" s="1" t="s">
@@ -6914,7 +6914,7 @@
         <v>147</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>70</v>
@@ -6937,7 +6937,7 @@
         <v>26</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U24" s="1"/>
       <c r="V24" s="1" t="s">
@@ -6988,7 +6988,7 @@
         <v>157</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>26</v>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7055,7 +7055,7 @@
         <v>26</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U26" s="1"/>
       <c r="V26" s="1" t="s">
@@ -7082,47 +7082,47 @@
         <v>27</v>
       </c>
       <c r="G27" s="1"/>
-      <c r="H27" s="1" t="s">
-        <v>170</v>
-      </c>
+      <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L27" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="M27" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>174</v>
-      </c>
       <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
+      <c r="Q27" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R27" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S27" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U27" s="1"/>
       <c r="V27" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B28" s="1">
         <v>27967686</v>
@@ -7131,7 +7131,7 @@
         <v>168</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>26</v>
@@ -7140,19 +7140,21 @@
         <v>27</v>
       </c>
       <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
+      <c r="H28" s="1" t="s">
+        <v>176</v>
+      </c>
       <c r="I28" s="1"/>
       <c r="J28" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K28" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="K28" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="L28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M28" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="N28" s="1" t="s">
         <v>27</v>
@@ -7161,17 +7163,15 @@
         <v>180</v>
       </c>
       <c r="P28" s="1"/>
-      <c r="Q28" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q28" s="1"/>
       <c r="R28" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S28" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U28" s="1"/>
       <c r="V28" s="1" t="s">
@@ -7206,31 +7206,47 @@
       <c r="I29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
+      <c r="J29" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>188</v>
+      </c>
       <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
+      <c r="Q29" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R29" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="U29" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U29" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="V29" s="1" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B30" s="1">
         <v>28073088</v>
@@ -7256,40 +7272,24 @@
       <c r="I30" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>190</v>
-      </c>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q30" s="1"/>
       <c r="R30" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S30" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>191</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="U30" s="1"/>
       <c r="V30" s="1" t="s">
         <v>192</v>
       </c>
@@ -7342,10 +7342,10 @@
       </c>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S31" s="1" t="s">
         <v>26</v>
@@ -7403,7 +7403,7 @@
         <v>26</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U32" s="1"/>
       <c r="V32" s="1" t="s">
@@ -7452,10 +7452,10 @@
       </c>
       <c r="P33" s="1"/>
       <c r="Q33" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
@@ -7484,7 +7484,7 @@
         <v>207</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>216</v>
@@ -7525,7 +7525,7 @@
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7546,7 +7546,7 @@
         <v>222</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>216</v>
@@ -7554,31 +7554,45 @@
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="J35" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>224</v>
+      </c>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
+      <c r="Q35" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R35" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S35" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U35" s="1"/>
       <c r="V35" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:22">
       <c r="A36" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B36" s="1">
         <v>31063506</v>
@@ -7590,7 +7604,7 @@
         <v>222</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>216</v>
@@ -7598,36 +7612,22 @@
       <c r="G36" s="1"/>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
-      <c r="J36" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>226</v>
-      </c>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q36" s="1"/>
       <c r="R36" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S36" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U36" s="1"/>
       <c r="V36" s="1" t="s">
@@ -7648,7 +7648,7 @@
         <v>230</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>231</v>
@@ -7660,45 +7660,31 @@
       <c r="I37" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B38" s="1">
         <v>31064850</v>
@@ -7710,34 +7696,48 @@
         <v>230</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>231</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="O38" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -7758,7 +7758,7 @@
         <v>245</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>246</v>
@@ -7766,45 +7766,31 @@
       <c r="G39" s="1"/>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
-      <c r="J39" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>248</v>
-      </c>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
       <c r="P39" s="1"/>
-      <c r="Q39" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q39" s="1"/>
       <c r="R39" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S39" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U39" s="1"/>
       <c r="V39" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="1:22">
       <c r="A40" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B40" s="1">
         <v>31092349</v>
@@ -7816,7 +7802,7 @@
         <v>245</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>246</v>
@@ -7824,22 +7810,36 @@
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+      <c r="J40" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>250</v>
+      </c>
       <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
+      <c r="Q40" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R40" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S40" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U40" s="1"/>
       <c r="V40" s="1" t="s">
@@ -7867,32 +7867,48 @@
       </c>
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
+      <c r="I41" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>259</v>
+      </c>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
+      <c r="Q41" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R41" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31124688</v>
@@ -7911,39 +7927,23 @@
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
-      <c r="I42" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>261</v>
-      </c>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="1"/>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="Q42" s="1"/>
       <c r="R42" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -7998,10 +7998,10 @@
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R44" s="1" t="s">
         <v>26</v>
@@ -8063,7 +8063,7 @@
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U44" s="1"/>
       <c r="V44" s="1" t="s">
@@ -8084,7 +8084,7 @@
         <v>280</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>281</v>
@@ -8107,7 +8107,7 @@
         <v>26</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U45" s="1"/>
       <c r="V45" s="1" t="s">
@@ -8128,7 +8128,7 @@
         <v>280</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>281</v>
@@ -8143,7 +8143,7 @@
         <v>217</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>280</v>
@@ -8159,7 +8159,7 @@
         <v>101</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S46" s="1" t="s">
         <v>26</v>
@@ -8218,10 +8218,10 @@
       </c>
       <c r="P47" s="1"/>
       <c r="Q47" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S47" s="1" t="s">
         <v>26</v>
@@ -8285,7 +8285,7 @@
         <v>26</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U48" s="1"/>
       <c r="V48" s="1" t="s">
@@ -8304,7 +8304,7 @@
         <v>301</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>302</v>
@@ -8335,7 +8335,7 @@
         <v>101</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S49" s="1" t="s">
         <v>26</v>
@@ -8360,7 +8360,7 @@
         <v>308</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>302</v>
@@ -8389,7 +8389,7 @@
         <v>26</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U50" s="1"/>
       <c r="V50" s="1" t="s">
@@ -8410,55 +8410,39 @@
         <v>312</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G51" s="1"/>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
-      <c r="J51" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="J51" s="1"/>
+      <c r="K51" s="1"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
       <c r="R51" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S51" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T51" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U51" s="1"/>
       <c r="V51" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="52" spans="1:22">
       <c r="A52" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B52" s="1">
         <v>31394760</v>
@@ -8470,30 +8454,46 @@
         <v>312</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+      <c r="J52" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="L52" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="N52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="P52" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R52" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S52" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U52" s="1"/>
       <c r="V52" s="1" t="s">
@@ -8514,7 +8514,7 @@
         <v>321</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>322</v>
@@ -8537,7 +8537,7 @@
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
@@ -8558,7 +8558,7 @@
         <v>321</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>322</v>
@@ -8581,7 +8581,7 @@
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -8602,7 +8602,7 @@
         <v>328</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>70</v>
@@ -8625,7 +8625,7 @@
         <v>26</v>
       </c>
       <c r="T55" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U55" s="1"/>
       <c r="V55" s="1" t="s">
@@ -8646,7 +8646,7 @@
         <v>328</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>70</v>
@@ -8675,7 +8675,7 @@
         <v>26</v>
       </c>
       <c r="T56" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U56" s="1"/>
       <c r="V56" s="1" t="s">
@@ -8696,55 +8696,39 @@
         <v>334</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
-      <c r="J57" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="L57" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>337</v>
-      </c>
-      <c r="P57" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="J57" s="1"/>
+      <c r="K57" s="1"/>
+      <c r="L57" s="1"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
       <c r="R57" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S57" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B58" s="1">
         <v>31445216</v>
@@ -8756,30 +8740,46 @@
         <v>334</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G58" s="1"/>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
+      <c r="J58" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="P58" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R58" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S58" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T58" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U58" s="1"/>
       <c r="V58" s="1" t="s">
@@ -8800,7 +8800,7 @@
         <v>344</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>231</v>
@@ -8812,7 +8812,7 @@
         <v>345</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L59" s="1"/>
       <c r="M59" s="1" t="s">
@@ -8826,10 +8826,10 @@
       </c>
       <c r="P59" s="1"/>
       <c r="Q59" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R59" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S59" s="1" t="s">
         <v>26</v>
@@ -8856,7 +8856,7 @@
         <v>344</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>231</v>
@@ -8879,7 +8879,7 @@
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
@@ -8900,7 +8900,7 @@
         <v>353</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>70</v>
@@ -8923,7 +8923,7 @@
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -8944,7 +8944,7 @@
         <v>353</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>70</v>
@@ -8967,7 +8967,7 @@
         <v>26</v>
       </c>
       <c r="T62" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U62" s="1"/>
       <c r="V62" s="1" t="s">
@@ -8988,53 +8988,41 @@
         <v>359</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>360</v>
       </c>
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1" t="s">
+      <c r="I63" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="K63" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>359</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>362</v>
-      </c>
+      <c r="J63" s="1"/>
+      <c r="K63" s="1"/>
+      <c r="L63" s="1"/>
+      <c r="M63" s="1"/>
+      <c r="N63" s="1"/>
+      <c r="O63" s="1"/>
       <c r="P63" s="1"/>
-      <c r="Q63" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q63" s="1"/>
       <c r="R63" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S63" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T63" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U63" s="1"/>
       <c r="V63" s="1" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="64" spans="1:22">
       <c r="A64" s="1" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B64" s="1">
         <v>31475270</v>
@@ -9046,32 +9034,44 @@
         <v>359</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="1"/>
+      <c r="J64" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="L64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="O64" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
       <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
+      <c r="Q64" s="1" t="s">
+        <v>101</v>
+      </c>
       <c r="R64" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S64" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T64" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U64" s="1"/>
       <c r="V64" s="1" t="s">
@@ -9092,10 +9092,10 @@
         <v>359</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
@@ -9115,7 +9115,7 @@
         <v>26</v>
       </c>
       <c r="T65" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U65" s="1"/>
       <c r="V65" s="1" t="s">
@@ -9146,7 +9146,7 @@
         <v>372</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L66" s="1"/>
       <c r="M66" s="1" t="s">
@@ -9162,10 +9162,10 @@
         <v>374</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R66" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S66" s="1" t="s">
         <v>26</v>
@@ -9190,7 +9190,7 @@
         <v>371</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>70</v>
@@ -9213,7 +9213,7 @@
         <v>26</v>
       </c>
       <c r="T67" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U67" s="1"/>
       <c r="V67" s="1" t="s">
@@ -9234,41 +9234,57 @@
         <v>380</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G68" s="1"/>
       <c r="H68" s="1" t="s">
         <v>381</v>
       </c>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
+      <c r="J68" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="L68" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="P68" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>52</v>
+      </c>
       <c r="R68" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S68" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U68" s="1"/>
       <c r="V68" s="1" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="1:22">
       <c r="A69" s="1" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="B69" s="1">
         <v>31489362</v>
@@ -9280,48 +9296,32 @@
         <v>380</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1" t="s">
         <v>381</v>
       </c>
       <c r="I69" s="1"/>
-      <c r="J69" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>387</v>
-      </c>
-      <c r="P69" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+      <c r="M69" s="1"/>
+      <c r="N69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1"/>
+      <c r="Q69" s="1"/>
       <c r="R69" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S69" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T69" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U69" s="1"/>
       <c r="V69" s="1" t="s">
@@ -9356,7 +9356,7 @@
         <v>393</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>394</v>
@@ -9374,10 +9374,10 @@
         <v>374</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R70" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S70" s="1" t="s">
         <v>26</v>
@@ -9406,7 +9406,7 @@
         <v>371</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>70</v>
@@ -9429,7 +9429,7 @@
         <v>26</v>
       </c>
       <c r="T71" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U71" s="1"/>
       <c r="V71" s="1" t="s">
@@ -9450,49 +9450,39 @@
         <v>401</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="G72" s="1"/>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
-      <c r="J72" s="1" t="s">
-        <v>400</v>
-      </c>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
-      <c r="M72" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>402</v>
-      </c>
+      <c r="M72" s="1"/>
+      <c r="N72" s="1"/>
+      <c r="O72" s="1"/>
       <c r="P72" s="1"/>
-      <c r="Q72" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="Q72" s="1"/>
       <c r="R72" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="S72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T72" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="U72" s="1"/>
       <c r="V72" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:22">
       <c r="A73" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B73" s="1">
         <v>31544182</v>
@@ -9504,30 +9494,40 @@
         <v>401</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
+      <c r="J73" s="1" t="s">
+        <v>400</v>
+      </c>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
+      <c r="M73" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>404</v>
+      </c>
       <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
+      <c r="Q73" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="R73" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="S73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T73" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="U73" s="1"/>
       <c r="V73" s="1" t="s">
@@ -9548,7 +9548,7 @@
         <v>408</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>246</v>
@@ -9571,7 +9571,7 @@
         <v>26</v>
       </c>
       <c r="T74" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U74" s="1"/>
       <c r="V74" s="1" t="s">
@@ -9592,7 +9592,7 @@
         <v>411</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>246</v>
@@ -9623,7 +9623,7 @@
         <v>101</v>
       </c>
       <c r="R75" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S75" s="1" t="s">
         <v>26</v>
@@ -9650,7 +9650,7 @@
         <v>418</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>70</v>
@@ -9673,7 +9673,7 @@
         <v>26</v>
       </c>
       <c r="T76" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U76" s="1"/>
       <c r="V76" s="1" t="s">
@@ -9706,7 +9706,7 @@
         <v>421</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L77" s="1" t="s">
         <v>422</v>
@@ -9725,7 +9725,7 @@
         <v>101</v>
       </c>
       <c r="R77" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S77" s="1" t="s">
         <v>26</v>
@@ -9750,7 +9750,7 @@
         <v>426</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>246</v>
@@ -9773,7 +9773,7 @@
         <v>26</v>
       </c>
       <c r="T78" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U78" s="1"/>
       <c r="V78" s="1" t="s">
@@ -9823,7 +9823,7 @@
         <v>101</v>
       </c>
       <c r="R79" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S79" s="1" t="s">
         <v>26</v>
@@ -9848,7 +9848,7 @@
         <v>435</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>436</v>
@@ -9885,7 +9885,7 @@
         <v>101</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S80" s="1" t="s">
         <v>26</v>
@@ -9944,10 +9944,10 @@
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R81" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S81" s="1" t="s">
         <v>26</v>
@@ -9998,10 +9998,10 @@
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R82" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S82" s="1" t="s">
         <v>26</v>
@@ -10060,10 +10060,10 @@
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R83" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S83" s="1" t="s">
         <v>26</v>
@@ -10116,10 +10116,10 @@
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R84" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S84" s="1" t="s">
         <v>26</v>
@@ -10142,7 +10142,7 @@
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>471</v>
@@ -10172,10 +10172,10 @@
         <v>476</v>
       </c>
       <c r="Q85" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R85" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S85" s="1" t="s">
         <v>26</v>
@@ -10230,10 +10230,10 @@
         <v>483</v>
       </c>
       <c r="Q86" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R86" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>26</v>
@@ -10294,10 +10294,10 @@
       </c>
       <c r="P87" s="1"/>
       <c r="Q87" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R87" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S87" s="1" t="s">
         <v>26</v>
@@ -10354,10 +10354,10 @@
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S88" s="1" t="s">
         <v>26</v>
@@ -10399,7 +10399,7 @@
         <v>503</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M89" s="1"/>
       <c r="N89" s="1" t="s">
@@ -10410,10 +10410,10 @@
       </c>
       <c r="P89" s="1"/>
       <c r="Q89" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R89" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S89" s="1" t="s">
         <v>26</v>
@@ -10455,7 +10455,7 @@
         <v>274</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>510</v>
@@ -10468,10 +10468,10 @@
       </c>
       <c r="P90" s="1"/>
       <c r="Q90" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R90" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S90" s="1" t="s">
         <v>26</v>
@@ -10496,7 +10496,7 @@
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>515</v>
@@ -10529,7 +10529,7 @@
         <v>101</v>
       </c>
       <c r="R91" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S91" s="1" t="s">
         <v>26</v>
@@ -10556,7 +10556,7 @@
         <v>523</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>471</v>
@@ -10572,10 +10572,10 @@
         <v>526</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>523</v>
@@ -10588,10 +10588,10 @@
       </c>
       <c r="P92" s="1"/>
       <c r="Q92" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R92" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S92" s="1" t="s">
         <v>26</v>
@@ -10646,10 +10646,10 @@
       </c>
       <c r="P93" s="1"/>
       <c r="Q93" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R93" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S93" s="1" t="s">
         <v>26</v>
@@ -10698,10 +10698,10 @@
       </c>
       <c r="P94" s="1"/>
       <c r="Q94" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R94" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S94" s="1" t="s">
         <v>26</v>
@@ -10759,7 +10759,7 @@
         <v>101</v>
       </c>
       <c r="R95" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S95" s="1" t="s">
         <v>26</v>
@@ -10784,7 +10784,7 @@
         <v>550</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>551</v>
@@ -10809,7 +10809,7 @@
         <v>26</v>
       </c>
       <c r="T96" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U96" s="1"/>
       <c r="V96" s="1" t="s">
@@ -10826,7 +10826,7 @@
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>555</v>
@@ -10847,7 +10847,7 @@
         <v>558</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>559</v>
@@ -10860,10 +10860,10 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R97" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S97" s="1" t="s">
         <v>26</v>
@@ -10888,7 +10888,7 @@
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F98" s="1" t="s">
         <v>216</v>
@@ -10917,7 +10917,7 @@
         <v>26</v>
       </c>
       <c r="T98" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U98" s="1" t="s">
         <v>566</v>
@@ -10936,7 +10936,7 @@
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>569</v>
@@ -10967,7 +10967,7 @@
         <v>101</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S99" s="1" t="s">
         <v>26</v>
@@ -11029,7 +11029,7 @@
         <v>101</v>
       </c>
       <c r="R100" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S100" s="1" t="s">
         <v>26</v>
@@ -11087,7 +11087,7 @@
         <v>101</v>
       </c>
       <c r="R101" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S101" s="1" t="s">
         <v>26</v>
@@ -11146,7 +11146,7 @@
         <v>596</v>
       </c>
       <c r="Q102" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R102" s="1" t="s">
         <v>26</v>
@@ -11155,7 +11155,7 @@
         <v>26</v>
       </c>
       <c r="T102" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U102" s="1"/>
       <c r="V102" s="1" t="s">
@@ -11195,7 +11195,7 @@
         <v>26</v>
       </c>
       <c r="T103" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U103" s="1" t="s">
         <v>599</v>
@@ -11216,7 +11216,7 @@
         <v>602</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>246</v>
@@ -11239,7 +11239,7 @@
         <v>26</v>
       </c>
       <c r="T104" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U104" s="1"/>
       <c r="V104" s="1" t="s">
@@ -11295,7 +11295,7 @@
         <v>101</v>
       </c>
       <c r="R105" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S105" s="1" t="s">
         <v>26</v>
@@ -11353,7 +11353,7 @@
         <v>101</v>
       </c>
       <c r="R106" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S106" s="1" t="s">
         <v>26</v>
@@ -11390,10 +11390,10 @@
         <v>619</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M107" s="1" t="s">
         <v>620</v>
@@ -11406,10 +11406,10 @@
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R107" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S107" s="1" t="s">
         <v>26</v>
@@ -11459,7 +11459,7 @@
         <v>26</v>
       </c>
       <c r="T108" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U108" s="1"/>
       <c r="V108" s="1" t="s">
@@ -11512,10 +11512,10 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R109" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S109" s="1" t="s">
         <v>26</v>
@@ -11542,7 +11542,7 @@
         <v>635</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>246</v>
@@ -11565,7 +11565,7 @@
         <v>26</v>
       </c>
       <c r="T110" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U110" s="1"/>
       <c r="V110" s="1" t="s">
@@ -11601,7 +11601,7 @@
         <v>58</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>638</v>
@@ -11614,10 +11614,10 @@
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R111" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S111" s="1" t="s">
         <v>26</v>
@@ -11669,7 +11669,7 @@
         <v>26</v>
       </c>
       <c r="T112" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U112" s="1"/>
       <c r="V112" s="1" t="s">
@@ -11718,10 +11718,10 @@
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R113" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S113" s="1" t="s">
         <v>26</v>
@@ -11761,7 +11761,7 @@
         <v>217</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>652</v>
@@ -11774,10 +11774,10 @@
       </c>
       <c r="P114" s="1"/>
       <c r="Q114" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R114" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S114" s="1" t="s">
         <v>26</v>
@@ -11832,10 +11832,10 @@
       </c>
       <c r="P115" s="1"/>
       <c r="Q115" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R115" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S115" s="1" t="s">
         <v>26</v>
@@ -11883,7 +11883,7 @@
         <v>26</v>
       </c>
       <c r="T116" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U116" s="1" t="s">
         <v>665</v>
@@ -11902,7 +11902,7 @@
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>668</v>
@@ -11934,10 +11934,10 @@
       </c>
       <c r="P117" s="1"/>
       <c r="Q117" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R117" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S117" s="1" t="s">
         <v>26</v>
@@ -11988,10 +11988,10 @@
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R118" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S118" s="1" t="s">
         <v>26</v>
@@ -12048,10 +12048,10 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R119" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S119" s="1" t="s">
         <v>26</v>
@@ -12076,7 +12076,7 @@
         <v>688</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>70</v>
@@ -12104,7 +12104,7 @@
         <v>692</v>
       </c>
       <c r="Q120" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R120" s="1" t="s">
         <v>26</v>
@@ -12113,7 +12113,7 @@
         <v>26</v>
       </c>
       <c r="T120" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U120" s="1"/>
       <c r="V120" s="1" t="s">
@@ -12160,10 +12160,10 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R121" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S121" s="1" t="s">
         <v>26</v>
@@ -12220,10 +12220,10 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R122" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S122" s="1" t="s">
         <v>26</v>
@@ -12271,7 +12271,7 @@
         <v>101</v>
       </c>
       <c r="R123" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S123" s="1" t="s">
         <v>26</v>
@@ -12294,7 +12294,7 @@
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>712</v>
@@ -12320,10 +12320,10 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R124" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S124" s="1" t="s">
         <v>26</v>
@@ -12346,10 +12346,10 @@
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G125" s="1"/>
       <c r="H125" s="1"/>
@@ -12369,7 +12369,7 @@
         <v>26</v>
       </c>
       <c r="T125" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U125" s="1"/>
       <c r="V125" s="1" t="s">
@@ -12386,10 +12386,10 @@
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G126" s="1" t="s">
         <v>28</v>
@@ -12415,7 +12415,7 @@
         <v>26</v>
       </c>
       <c r="T126" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U126" s="1"/>
       <c r="V126" s="1" t="s">
@@ -12455,7 +12455,7 @@
         <v>26</v>
       </c>
       <c r="T127" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U127" s="1"/>
       <c r="V127" s="1" t="s">
@@ -12506,10 +12506,10 @@
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R128" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S128" s="1" t="s">
         <v>26</v>
@@ -12560,10 +12560,10 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R129" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S129" s="1" t="s">
         <v>26</v>
@@ -12615,7 +12615,7 @@
         <v>101</v>
       </c>
       <c r="R130" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S130" s="1" t="s">
         <v>26</v>
@@ -12638,7 +12638,7 @@
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>740</v>
@@ -12669,7 +12669,7 @@
         <v>101</v>
       </c>
       <c r="R131" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S131" s="1" t="s">
         <v>26</v>
@@ -12692,7 +12692,7 @@
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>569</v>
@@ -12717,7 +12717,7 @@
         <v>26</v>
       </c>
       <c r="T132" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U132" s="1"/>
       <c r="V132" s="1" t="s">
@@ -12734,10 +12734,10 @@
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G133" s="1"/>
       <c r="H133" s="1"/>
@@ -12749,13 +12749,13 @@
         <v>750</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>751</v>
       </c>
       <c r="N133" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O133" s="1" t="s">
         <v>752</v>
@@ -12765,7 +12765,7 @@
         <v>101</v>
       </c>
       <c r="R133" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S133" s="1" t="s">
         <v>26</v>
@@ -12822,10 +12822,10 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R134" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S134" s="1" t="s">
         <v>26</v>
@@ -12848,7 +12848,7 @@
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>216</v>
@@ -12877,7 +12877,7 @@
         <v>101</v>
       </c>
       <c r="R135" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S135" s="1" t="s">
         <v>26</v>
@@ -12936,10 +12936,10 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R136" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S136" s="1" t="s">
         <v>26</v>
@@ -12990,10 +12990,10 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R137" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S137" s="1" t="s">
         <v>26</v>
@@ -13037,7 +13037,7 @@
         <v>274</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>781</v>
@@ -13050,10 +13050,10 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R138" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S138" s="1" t="s">
         <v>26</v>
@@ -13076,7 +13076,7 @@
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>471</v>
@@ -13088,7 +13088,7 @@
         <v>785</v>
       </c>
       <c r="K139" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L139" s="1" t="s">
         <v>210</v>
@@ -13104,10 +13104,10 @@
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R139" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S139" s="1" t="s">
         <v>26</v>
@@ -13130,10 +13130,10 @@
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G140" s="1"/>
       <c r="H140" s="1"/>
@@ -13151,7 +13151,7 @@
         <v>792</v>
       </c>
       <c r="N140" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O140" s="1" t="s">
         <v>793</v>
@@ -13161,7 +13161,7 @@
         <v>101</v>
       </c>
       <c r="R140" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S140" s="1" t="s">
         <v>26</v>
@@ -13184,7 +13184,7 @@
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>302</v>
@@ -13213,7 +13213,7 @@
         <v>26</v>
       </c>
       <c r="T141" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U141" s="1"/>
       <c r="V141" s="1" t="s">
@@ -13230,7 +13230,7 @@
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>302</v>
@@ -13258,10 +13258,10 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R142" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S142" s="1" t="s">
         <v>26</v>
@@ -13284,7 +13284,7 @@
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>807</v>
@@ -13316,10 +13316,10 @@
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R143" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S143" s="1" t="s">
         <v>26</v>
@@ -13342,10 +13342,10 @@
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1"/>
@@ -13365,7 +13365,7 @@
         <v>26</v>
       </c>
       <c r="T144" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U144" s="1"/>
       <c r="V144" s="1" t="s">
@@ -13416,10 +13416,10 @@
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R145" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S145" s="1" t="s">
         <v>26</v>
@@ -13480,10 +13480,10 @@
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R146" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S146" s="1" t="s">
         <v>26</v>
@@ -13506,7 +13506,7 @@
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>216</v>
@@ -13532,10 +13532,10 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R147" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S147" s="1" t="s">
         <v>26</v>
@@ -13560,7 +13560,7 @@
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>471</v>
@@ -13583,7 +13583,7 @@
         <v>26</v>
       </c>
       <c r="T148" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U148" s="1" t="s">
         <v>835</v>
@@ -13604,7 +13604,7 @@
         <v>838</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>302</v>
@@ -13629,7 +13629,7 @@
         <v>26</v>
       </c>
       <c r="T149" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U149" s="1" t="s">
         <v>840</v>
@@ -13650,7 +13650,7 @@
         <v>843</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>231</v>
@@ -13684,10 +13684,10 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R150" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S150" s="1" t="s">
         <v>26</v>
@@ -13723,10 +13723,10 @@
       </c>
       <c r="I151" s="1"/>
       <c r="J151" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K151" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L151" s="1" t="s">
         <v>850</v>
@@ -13742,10 +13742,10 @@
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R151" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S151" s="1" t="s">
         <v>26</v>
@@ -13770,7 +13770,7 @@
         <v>854</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>855</v>
@@ -13801,7 +13801,7 @@
         <v>101</v>
       </c>
       <c r="R152" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S152" s="1" t="s">
         <v>26</v>
@@ -13826,7 +13826,7 @@
         <v>862</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>863</v>
@@ -13841,7 +13841,7 @@
         <v>857</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M153" s="1" t="s">
         <v>862</v>
@@ -13854,10 +13854,10 @@
       </c>
       <c r="P153" s="1"/>
       <c r="Q153" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R153" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S153" s="1" t="s">
         <v>26</v>
@@ -13901,7 +13901,7 @@
         <v>274</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>869</v>
@@ -13914,10 +13914,10 @@
       </c>
       <c r="P154" s="1"/>
       <c r="Q154" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R154" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S154" s="1" t="s">
         <v>26</v>
@@ -13970,10 +13970,10 @@
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R155" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S155" s="1" t="s">
         <v>26</v>
@@ -13998,7 +13998,7 @@
         <v>881</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>231</v>
@@ -14015,7 +14015,7 @@
         <v>80</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M156" s="1" t="s">
         <v>881</v>
@@ -14031,7 +14031,7 @@
         <v>101</v>
       </c>
       <c r="R156" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S156" s="1" t="s">
         <v>26</v>
@@ -14056,10 +14056,10 @@
         <v>887</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G157" s="1" t="s">
         <v>28</v>
@@ -14083,17 +14083,17 @@
         <v>887</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O157" s="1" t="s">
         <v>891</v>
       </c>
       <c r="P157" s="1"/>
       <c r="Q157" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R157" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S157" s="1" t="s">
         <v>26</v>
@@ -14152,10 +14152,10 @@
       </c>
       <c r="P158" s="1"/>
       <c r="Q158" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R158" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S158" s="1" t="s">
         <v>26</v>
@@ -14213,7 +14213,7 @@
         <v>101</v>
       </c>
       <c r="R159" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S159" s="1" t="s">
         <v>26</v>
@@ -14238,7 +14238,7 @@
         <v>906</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>302</v>
@@ -14267,7 +14267,7 @@
         <v>26</v>
       </c>
       <c r="T160" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U160" s="1"/>
       <c r="V160" s="1" t="s">
@@ -14312,10 +14312,10 @@
       </c>
       <c r="P161" s="1"/>
       <c r="Q161" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R161" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S161" s="1" t="s">
         <v>26</v>
@@ -14340,7 +14340,7 @@
         <v>914</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>471</v>
@@ -14355,7 +14355,7 @@
         <v>58</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1" t="s">
@@ -14366,7 +14366,7 @@
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>26</v>
@@ -14375,7 +14375,7 @@
         <v>26</v>
       </c>
       <c r="T162" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U162" s="1"/>
       <c r="V162" s="1" t="s">
@@ -14419,7 +14419,7 @@
         <v>26</v>
       </c>
       <c r="T163" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U163" s="1" t="s">
         <v>599</v>
@@ -14470,7 +14470,7 @@
       </c>
       <c r="P164" s="1"/>
       <c r="Q164" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R164" s="1" t="s">
         <v>26</v>
@@ -14515,7 +14515,7 @@
         <v>274</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M165" s="1"/>
       <c r="N165" s="1" t="s">
@@ -14526,10 +14526,10 @@
       </c>
       <c r="P165" s="1"/>
       <c r="Q165" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R165" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S165" s="1" t="s">
         <v>26</v>
@@ -14552,7 +14552,7 @@
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>302</v>
@@ -14581,7 +14581,7 @@
         <v>26</v>
       </c>
       <c r="T166" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U166" s="1" t="s">
         <v>936</v>
@@ -14602,7 +14602,7 @@
         <v>939</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>246</v>
@@ -14630,10 +14630,10 @@
       </c>
       <c r="P167" s="1"/>
       <c r="Q167" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R167" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S167" s="1" t="s">
         <v>26</v>
@@ -14656,7 +14656,7 @@
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>944</v>
@@ -14682,10 +14682,10 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R168" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S168" s="1" t="s">
         <v>26</v>
@@ -14710,7 +14710,7 @@
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>216</v>
@@ -14739,7 +14739,7 @@
         <v>101</v>
       </c>
       <c r="R169" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S169" s="1" t="s">
         <v>26</v>
@@ -14795,7 +14795,7 @@
         <v>26</v>
       </c>
       <c r="T170" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U170" s="1"/>
       <c r="V170" s="1" t="s">
@@ -14846,10 +14846,10 @@
       </c>
       <c r="P171" s="1"/>
       <c r="Q171" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R171" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S171" s="1" t="s">
         <v>26</v>
@@ -14905,7 +14905,7 @@
         <v>101</v>
       </c>
       <c r="R172" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S172" s="1" t="s">
         <v>26</v>
@@ -14969,7 +14969,7 @@
         <v>26</v>
       </c>
       <c r="T173" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U173" s="1" t="s">
         <v>980</v>
@@ -15016,13 +15016,13 @@
       </c>
       <c r="P174" s="1"/>
       <c r="Q174" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S174" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T174" s="1" t="s">
         <v>26</v>
@@ -15078,10 +15078,10 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R175" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S175" s="1" t="s">
         <v>26</v>
@@ -15108,7 +15108,7 @@
         <v>997</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>998</v>
@@ -15144,10 +15144,10 @@
         <v>1003</v>
       </c>
       <c r="Q176" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R176" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S176" s="1" t="s">
         <v>26</v>
@@ -15172,7 +15172,7 @@
         <v>1006</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>322</v>
@@ -15195,7 +15195,7 @@
         <v>26</v>
       </c>
       <c r="T177" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U177" s="1"/>
       <c r="V177" s="1" t="s">
@@ -15214,7 +15214,7 @@
         <v>1009</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>668</v>
@@ -15243,7 +15243,7 @@
         <v>101</v>
       </c>
       <c r="R178" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S178" s="1" t="s">
         <v>26</v>
@@ -15287,7 +15287,7 @@
         <v>163</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M179" s="1" t="s">
         <v>1019</v>
@@ -15303,7 +15303,7 @@
         <v>101</v>
       </c>
       <c r="R179" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S179" s="1" t="s">
         <v>26</v>
@@ -15326,10 +15326,10 @@
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>28</v>
@@ -15353,20 +15353,20 @@
         <v>1025</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>1026</v>
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R180" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S180" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T180" s="1" t="s">
         <v>26</v>
@@ -15390,7 +15390,7 @@
         <v>1030</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>555</v>
@@ -15407,7 +15407,7 @@
         <v>1033</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M181" s="1" t="s">
         <v>1034</v>
@@ -15420,10 +15420,10 @@
       </c>
       <c r="P181" s="1"/>
       <c r="Q181" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R181" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S181" s="1" t="s">
         <v>26</v>
@@ -15480,10 +15480,10 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R182" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S182" s="1" t="s">
         <v>26</v>
@@ -15529,7 +15529,7 @@
         <v>26</v>
       </c>
       <c r="T183" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U183" s="1" t="s">
         <v>1045</v>
@@ -15573,7 +15573,7 @@
         <v>26</v>
       </c>
       <c r="T184" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U184" s="1" t="s">
         <v>1048</v>
@@ -15594,7 +15594,7 @@
         <v>1051</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>668</v>
@@ -15623,7 +15623,7 @@
         <v>26</v>
       </c>
       <c r="T185" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U185" s="1"/>
       <c r="V185" s="1" t="s">
@@ -15661,7 +15661,7 @@
         <v>58</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M186" s="1" t="s">
         <v>265</v>
@@ -15674,10 +15674,10 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R186" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S186" s="1" t="s">
         <v>26</v>
@@ -15730,10 +15730,10 @@
       </c>
       <c r="P187" s="1"/>
       <c r="Q187" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R187" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S187" s="1" t="s">
         <v>26</v>
@@ -15775,7 +15775,7 @@
         <v>857</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M188" s="1"/>
       <c r="N188" s="1" t="s">
@@ -15792,7 +15792,7 @@
         <v>26</v>
       </c>
       <c r="S188" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T188" s="1" t="s">
         <v>26</v>
@@ -15816,7 +15816,7 @@
         <v>1071</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>246</v>
@@ -15844,10 +15844,10 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R189" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S189" s="1" t="s">
         <v>26</v>
@@ -15872,7 +15872,7 @@
         <v>1076</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>246</v>
@@ -15906,10 +15906,10 @@
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R190" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S190" s="1" t="s">
         <v>26</v>
@@ -15953,7 +15953,7 @@
         <v>274</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1084</v>
@@ -15966,10 +15966,10 @@
       </c>
       <c r="P191" s="1"/>
       <c r="Q191" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R191" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S191" s="1" t="s">
         <v>26</v>
@@ -15994,7 +15994,7 @@
         <v>1091</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>302</v>
@@ -16030,10 +16030,10 @@
         <v>1096</v>
       </c>
       <c r="Q192" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R192" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S192" s="1" t="s">
         <v>26</v>
@@ -16060,7 +16060,7 @@
         <v>1099</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>302</v>
@@ -16079,7 +16079,7 @@
         <v>452</v>
       </c>
       <c r="L193" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M193" s="1" t="s">
         <v>1099</v>
@@ -16095,7 +16095,7 @@
         <v>101</v>
       </c>
       <c r="R193" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S193" s="1" t="s">
         <v>26</v>
@@ -16120,7 +16120,7 @@
         <v>1105</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F194" s="1" t="s">
         <v>436</v>
@@ -16154,10 +16154,10 @@
       </c>
       <c r="P194" s="1"/>
       <c r="Q194" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R194" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S194" s="1" t="s">
         <v>26</v>
@@ -16182,7 +16182,7 @@
         <v>1112</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>1113</v>
@@ -16217,7 +16217,7 @@
         <v>101</v>
       </c>
       <c r="R195" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S195" s="1" t="s">
         <v>26</v>
@@ -16276,10 +16276,10 @@
       </c>
       <c r="P196" s="1"/>
       <c r="Q196" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R196" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S196" s="1" t="s">
         <v>26</v>
@@ -16387,7 +16387,7 @@
         <v>58</v>
       </c>
       <c r="L198" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M198" s="1" t="s">
         <v>1136</v>
@@ -16403,7 +16403,7 @@
         <v>101</v>
       </c>
       <c r="R198" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S198" s="1" t="s">
         <v>26</v>
@@ -16465,7 +16465,7 @@
         <v>101</v>
       </c>
       <c r="R199" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S199" s="1" t="s">
         <v>26</v>
@@ -16514,13 +16514,13 @@
       </c>
       <c r="P200" s="1"/>
       <c r="Q200" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R200" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S200" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T200" s="1" t="s">
         <v>26</v>
@@ -16542,7 +16542,7 @@
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F201" s="1" t="s">
         <v>302</v>
@@ -16567,7 +16567,7 @@
         <v>26</v>
       </c>
       <c r="T201" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U201" s="1" t="s">
         <v>1154</v>
@@ -16586,10 +16586,10 @@
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G202" s="1"/>
       <c r="H202" s="1"/>
@@ -16609,7 +16609,7 @@
         <v>26</v>
       </c>
       <c r="T202" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U202" s="1" t="s">
         <v>1157</v>
@@ -16645,7 +16645,7 @@
         <v>1162</v>
       </c>
       <c r="L203" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M203" s="1"/>
       <c r="N203" s="1" t="s">
@@ -16656,10 +16656,10 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R203" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S203" s="1" t="s">
         <v>26</v>
@@ -16684,7 +16684,7 @@
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>302</v>
@@ -16710,13 +16710,13 @@
       </c>
       <c r="P204" s="1"/>
       <c r="Q204" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R204" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S204" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T204" s="1" t="s">
         <v>26</v>
@@ -16767,7 +16767,7 @@
         <v>101</v>
       </c>
       <c r="R205" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S205" s="1" t="s">
         <v>26</v>
@@ -16792,7 +16792,7 @@
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>1178</v>
@@ -16815,7 +16815,7 @@
         <v>26</v>
       </c>
       <c r="T206" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U206" s="1" t="s">
         <v>1179</v>
@@ -16869,10 +16869,10 @@
         <v>101</v>
       </c>
       <c r="R207" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S207" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T207" s="1" t="s">
         <v>26</v>
@@ -16913,7 +16913,7 @@
         <v>1190</v>
       </c>
       <c r="L208" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="M208" s="1" t="s">
         <v>1187</v>
@@ -16926,10 +16926,10 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R208" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S208" s="1" t="s">
         <v>26</v>
@@ -16990,10 +16990,10 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R209" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S209" s="1" t="s">
         <v>26</v>
@@ -17018,7 +17018,7 @@
         <v>1200</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>302</v>
@@ -17057,7 +17057,7 @@
         <v>26</v>
       </c>
       <c r="T210" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U210" s="1" t="s">
         <v>980</v>
@@ -17099,7 +17099,7 @@
         <v>1210</v>
       </c>
       <c r="L211" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M211" s="1" t="s">
         <v>1207</v>
@@ -17114,10 +17114,10 @@
         <v>1212</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R211" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S211" s="1" t="s">
         <v>26</v>
@@ -17142,10 +17142,10 @@
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G212" s="1"/>
       <c r="H212" s="1"/>
@@ -17157,21 +17157,21 @@
         <v>217</v>
       </c>
       <c r="L212" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M212" s="1"/>
       <c r="N212" s="1" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>1217</v>
       </c>
       <c r="P212" s="1"/>
       <c r="Q212" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R212" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S212" s="1" t="s">
         <v>26</v>
@@ -17196,7 +17196,7 @@
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F213" s="1" t="s">
         <v>302</v>
@@ -17225,7 +17225,7 @@
         <v>26</v>
       </c>
       <c r="T213" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U213" s="1" t="s">
         <v>936</v>
@@ -17246,7 +17246,7 @@
         <v>1223</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F214" s="1" t="s">
         <v>70</v>
@@ -17275,7 +17275,7 @@
         <v>26</v>
       </c>
       <c r="T214" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U214" s="1"/>
       <c r="V214" s="1" t="s">
@@ -17294,7 +17294,7 @@
         <v>1227</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F215" s="1" t="s">
         <v>1228</v>
@@ -17312,7 +17312,7 @@
         <v>1230</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L215" s="1" t="s">
         <v>1231</v>
@@ -17328,10 +17328,10 @@
       </c>
       <c r="P215" s="1"/>
       <c r="Q215" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R215" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S215" s="1" t="s">
         <v>26</v>
@@ -17358,7 +17358,7 @@
         <v>1237</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F216" s="1" t="s">
         <v>216</v>
@@ -17388,10 +17388,10 @@
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R216" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S216" s="1" t="s">
         <v>26</v>
@@ -17420,7 +17420,7 @@
         <v>1237</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F217" s="1" t="s">
         <v>216</v>
@@ -17454,13 +17454,13 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R217" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S217" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T217" s="1" t="s">
         <v>26</v>
@@ -17486,7 +17486,7 @@
         <v>1247</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F218" s="1" t="s">
         <v>1228</v>
@@ -17511,7 +17511,7 @@
         <v>26</v>
       </c>
       <c r="T218" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U218" s="1"/>
       <c r="V218" s="1" t="s">
@@ -17532,7 +17532,7 @@
         <v>1247</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>1228</v>
@@ -17562,10 +17562,10 @@
       </c>
       <c r="P219" s="1"/>
       <c r="Q219" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R219" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S219" s="1" t="s">
         <v>26</v>
@@ -17607,7 +17607,7 @@
         <v>1258</v>
       </c>
       <c r="L220" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M220" s="1" t="s">
         <v>1259</v>
@@ -17620,10 +17620,10 @@
       </c>
       <c r="P220" s="1"/>
       <c r="Q220" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R220" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S220" s="1" t="s">
         <v>26</v>
@@ -17671,7 +17671,7 @@
         <v>1265</v>
       </c>
       <c r="L221" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="M221" s="1" t="s">
         <v>1266</v>
@@ -17684,10 +17684,10 @@
       </c>
       <c r="P221" s="1"/>
       <c r="Q221" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R221" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S221" s="1" t="s">
         <v>26</v>
@@ -17744,13 +17744,13 @@
       </c>
       <c r="P222" s="1"/>
       <c r="Q222" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R222" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S222" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T222" s="1" t="s">
         <v>26</v>
@@ -17804,13 +17804,13 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R223" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S223" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T223" s="1" t="s">
         <v>26</v>
@@ -17868,13 +17868,13 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R224" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S224" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T224" s="1" t="s">
         <v>26</v>
@@ -17932,13 +17932,13 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R225" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S225" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T225" s="1" t="s">
         <v>26</v>
@@ -17992,13 +17992,13 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R226" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S226" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T226" s="1" t="s">
         <v>26</v>
@@ -18055,7 +18055,7 @@
         <v>101</v>
       </c>
       <c r="R227" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S227" s="1" t="s">
         <v>26</v>
@@ -18112,10 +18112,10 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R228" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S228" s="1" t="s">
         <v>26</v>
@@ -18163,7 +18163,7 @@
         <v>163</v>
       </c>
       <c r="L229" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M229" s="1" t="s">
         <v>1321</v>
@@ -18176,16 +18176,16 @@
       </c>
       <c r="P229" s="1"/>
       <c r="Q229" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R229" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S229" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T229" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U229" s="1" t="s">
         <v>1323</v>
@@ -18245,7 +18245,7 @@
         <v>101</v>
       </c>
       <c r="R230" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S230" s="1" t="s">
         <v>26</v>
@@ -18302,10 +18302,10 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R231" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S231" s="1" t="s">
         <v>26</v>
@@ -18370,10 +18370,10 @@
         <v>1348</v>
       </c>
       <c r="Q232" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R232" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S232" s="1" t="s">
         <v>26</v>
@@ -18437,7 +18437,7 @@
         <v>101</v>
       </c>
       <c r="R233" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S233" s="1" t="s">
         <v>26</v>
@@ -18482,7 +18482,7 @@
         <v>1361</v>
       </c>
       <c r="K234" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="L234" s="1" t="s">
         <v>1362</v>
@@ -18498,10 +18498,10 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R234" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S234" s="1" t="s">
         <v>26</v>
@@ -18564,10 +18564,10 @@
       </c>
       <c r="P235" s="1"/>
       <c r="Q235" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R235" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S235" s="1" t="s">
         <v>26</v>
@@ -18625,7 +18625,7 @@
         <v>101</v>
       </c>
       <c r="R236" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S236" s="1" t="s">
         <v>26</v>
@@ -18668,7 +18668,7 @@
         <v>1384</v>
       </c>
       <c r="K237" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L237" s="1" t="s">
         <v>1337</v>
@@ -18687,13 +18687,13 @@
         <v>101</v>
       </c>
       <c r="R237" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S237" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T237" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U237" s="1" t="s">
         <v>1387</v>
@@ -18716,7 +18716,7 @@
         <v>1283</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F238" s="1" t="s">
         <v>231</v>
@@ -18746,10 +18746,10 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R238" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S238" s="1" t="s">
         <v>26</v>
@@ -18808,10 +18808,10 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R239" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S239" s="1" t="s">
         <v>26</v>
@@ -18872,10 +18872,10 @@
       </c>
       <c r="P240" s="1"/>
       <c r="Q240" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R240" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S240" s="1" t="s">
         <v>26</v>
@@ -18936,10 +18936,10 @@
       </c>
       <c r="P241" s="1"/>
       <c r="Q241" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R241" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S241" s="1" t="s">
         <v>26</v>
@@ -18999,7 +18999,7 @@
         <v>101</v>
       </c>
       <c r="R242" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S242" s="1" t="s">
         <v>26</v>
@@ -19056,16 +19056,16 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>26</v>
       </c>
       <c r="S243" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="T243" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U243" s="1" t="s">
         <v>61</v>
@@ -19116,10 +19116,10 @@
       </c>
       <c r="P244" s="1"/>
       <c r="Q244" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R244" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S244" s="1" t="s">
         <v>26</v>
@@ -19180,10 +19180,10 @@
       </c>
       <c r="P245" s="1"/>
       <c r="Q245" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R245" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S245" s="1" t="s">
         <v>26</v>
@@ -19242,16 +19242,16 @@
         <v>1441</v>
       </c>
       <c r="Q246" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R246" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S246" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T246" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U246" s="1" t="s">
         <v>1323</v>
@@ -19306,10 +19306,10 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R247" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S247" s="1" t="s">
         <v>26</v>
@@ -19352,10 +19352,10 @@
         <v>1456</v>
       </c>
       <c r="K248" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L248" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M248" s="1" t="s">
         <v>1454</v>
@@ -19371,7 +19371,7 @@
         <v>101</v>
       </c>
       <c r="R248" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S248" s="1" t="s">
         <v>26</v>
@@ -19412,10 +19412,10 @@
         <v>1460</v>
       </c>
       <c r="K249" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L249" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="M249" s="1" t="s">
         <v>1454</v>
@@ -19431,7 +19431,7 @@
         <v>101</v>
       </c>
       <c r="R249" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S249" s="1" t="s">
         <v>26</v>
@@ -19493,7 +19493,7 @@
         <v>101</v>
       </c>
       <c r="R250" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S250" s="1" t="s">
         <v>26</v>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="P251" s="1"/>
       <c r="Q251" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R251" s="1" t="s">
         <v>26</v>
@@ -19594,10 +19594,10 @@
         <v>1483</v>
       </c>
       <c r="K252" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>1482</v>
@@ -19610,10 +19610,10 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R252" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S252" s="1" t="s">
         <v>26</v>
@@ -19652,10 +19652,10 @@
         <v>1483</v>
       </c>
       <c r="K253" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>1487</v>
@@ -19668,10 +19668,10 @@
       </c>
       <c r="P253" s="1"/>
       <c r="Q253" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R253" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S253" s="1" t="s">
         <v>26</v>
@@ -19726,10 +19726,10 @@
       </c>
       <c r="P254" s="1"/>
       <c r="Q254" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R254" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S254" s="1" t="s">
         <v>26</v>
@@ -19786,10 +19786,10 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R255" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S255" s="1" t="s">
         <v>26</v>
@@ -19851,7 +19851,7 @@
         <v>101</v>
       </c>
       <c r="R256" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S256" s="1" t="s">
         <v>26</v>
@@ -19915,7 +19915,7 @@
         <v>101</v>
       </c>
       <c r="R257" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S257" s="1" t="s">
         <v>26</v>
@@ -19944,7 +19944,7 @@
         <v>1520</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>1521</v>
@@ -19975,7 +19975,7 @@
         <v>101</v>
       </c>
       <c r="R258" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S258" s="1" t="s">
         <v>26</v>
@@ -20002,7 +20002,7 @@
         <v>1527</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>1528</v>
@@ -20036,10 +20036,10 @@
       </c>
       <c r="P259" s="1"/>
       <c r="Q259" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R259" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S259" s="1" t="s">
         <v>26</v>
@@ -20100,10 +20100,10 @@
       </c>
       <c r="P260" s="1"/>
       <c r="Q260" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R260" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S260" s="1" t="s">
         <v>26</v>
@@ -20144,7 +20144,7 @@
         <v>1543</v>
       </c>
       <c r="K261" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L261" s="1" t="s">
         <v>210</v>
@@ -20160,10 +20160,10 @@
       </c>
       <c r="P261" s="1"/>
       <c r="Q261" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R261" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S261" s="1" t="s">
         <v>26</v>
@@ -20211,7 +20211,7 @@
         <v>1553</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>1554</v>
@@ -20227,7 +20227,7 @@
         <v>101</v>
       </c>
       <c r="R262" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S262" s="1" t="s">
         <v>26</v>
@@ -20287,7 +20287,7 @@
         <v>101</v>
       </c>
       <c r="R263" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S263" s="1" t="s">
         <v>26</v>
@@ -20346,10 +20346,10 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R264" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S264" s="1" t="s">
         <v>26</v>
@@ -20408,10 +20408,10 @@
       </c>
       <c r="P265" s="1"/>
       <c r="Q265" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R265" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S265" s="1" t="s">
         <v>26</v>
@@ -20440,7 +20440,7 @@
         <v>1578</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F266" s="1" t="s">
         <v>231</v>
@@ -20458,7 +20458,7 @@
         <v>1580</v>
       </c>
       <c r="K266" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L266" s="1" t="s">
         <v>1581</v>
@@ -20479,7 +20479,7 @@
         <v>101</v>
       </c>
       <c r="R266" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S266" s="1" t="s">
         <v>26</v>
@@ -20508,7 +20508,7 @@
         <v>1587</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>231</v>
@@ -20526,7 +20526,7 @@
         <v>1580</v>
       </c>
       <c r="K267" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L267" s="1" t="s">
         <v>1581</v>
@@ -20547,7 +20547,7 @@
         <v>101</v>
       </c>
       <c r="R267" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S267" s="1" t="s">
         <v>26</v>
@@ -20604,10 +20604,10 @@
       </c>
       <c r="P268" s="1"/>
       <c r="Q268" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R268" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S268" s="1" t="s">
         <v>26</v>
@@ -20671,7 +20671,7 @@
         <v>101</v>
       </c>
       <c r="R269" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S269" s="1" t="s">
         <v>26</v>
@@ -20714,10 +20714,10 @@
         <v>1608</v>
       </c>
       <c r="K270" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1609</v>
@@ -20730,10 +20730,10 @@
       </c>
       <c r="P270" s="1"/>
       <c r="Q270" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R270" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S270" s="1" t="s">
         <v>26</v>
@@ -20777,7 +20777,7 @@
         <v>857</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1614</v>
@@ -20790,10 +20790,10 @@
       </c>
       <c r="P271" s="1"/>
       <c r="Q271" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R271" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S271" s="1" t="s">
         <v>26</v>
@@ -20852,10 +20852,10 @@
       </c>
       <c r="P272" s="1"/>
       <c r="Q272" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R272" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S272" s="1" t="s">
         <v>26</v>
@@ -20916,10 +20916,10 @@
       </c>
       <c r="P273" s="1"/>
       <c r="Q273" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R273" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S273" s="1" t="s">
         <v>26</v>
@@ -20948,7 +20948,7 @@
         <v>1637</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>70</v>
@@ -20971,7 +20971,7 @@
         <v>26</v>
       </c>
       <c r="T274" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U274" s="1"/>
       <c r="V274" s="1" t="s">
@@ -21022,10 +21022,10 @@
       </c>
       <c r="P275" s="1"/>
       <c r="Q275" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="R275" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S275" s="1" t="s">
         <v>26</v>
@@ -21084,16 +21084,16 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R276" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S276" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T276" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U276" s="1" t="s">
         <v>1657</v>
@@ -21152,10 +21152,10 @@
         <v>1666</v>
       </c>
       <c r="Q277" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="R277" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="S277" s="1" t="s">
         <v>26</v>
